--- a/tests/data/api_movie.xlsx
+++ b/tests/data/api_movie.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jmlim\OneDrive\Desktop\PlaywrightQA\tests\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E383BF62-8AE4-4C45-87C9-FD12D5DA750A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{528E23FF-52F8-45B4-BBDD-C9EAA2F356C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1536" yWindow="1536" windowWidth="25752" windowHeight="14784" xr2:uid="{BDD45D70-0979-4E5A-A8FD-2688E650F3D3}"/>
+    <workbookView xWindow="3780" yWindow="2556" windowWidth="25752" windowHeight="14784" xr2:uid="{BDD45D70-0979-4E5A-A8FD-2688E650F3D3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
   <si>
     <t>movie_id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -78,14 +78,234 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>dream within a dream</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Inception</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft GothicNeo"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>2014-11-05</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>"</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft GothicNeo"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>2010-07-15</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>"</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft GothicNeo"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>1972-03-14</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>"</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>Interstellar</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> "시실리에서 이민온 뒤, 정치권까지 영향력을 미치는 거물로 자리잡은 돈 꼴레오네는 갖가지 고민을 호소하는 사람들의 문제를 해결해주며 대부라 불리운다. 한편 솔로소라는 인물은 꼴레오네가와 라이벌인 탓타리아 패밀리와 손잡고 새로운 마약 사업을 제안한다. 돈 꼴레오네가 마약 사업에 참여하지 않기로 하자, 돈 꼴레 오네를 저격해 그는 중상을 입고 사경을 헤매게 된다. 그 뒤, 돈 꼴레오네의 아들 소니는 조직력을 총 동원해 다른 패밀리들과 피를 부르는 전쟁을 시작하는데... 가족의 사업과 상관없이 대학에 진학한 뒤 인텔리로 지내왔던 막내 아들 마이클은 아버지가 총격을 당한 뒤, 아버지를 구하기 위해 위험천만한 협상 자리에 나선다."</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> "세계 각국의 정부와 경제가 완전히 붕괴된 미래가 다가온다. 지난 20세기에 범한 잘못이 전 세계적인 식량 부족을 불러왔고, NASA도 해체되었다. 나사 소속 우주비행사였던 쿠퍼는 지구에 몰아친 식량난으로 옥수수나 키우며 살고 있다. 거센 황사가 몰아친 어느 날 알 수 없는 힘에 이끌려 딸과 함께 도착한 곳은 인류가 이주할 행성을 찾는 나사의 비밀본부. 이 때 시공간에 불가사의한 틈이 열리고, 이 곳을 탐험해 인류를 구해야 하는 임무를 위해 쿠퍼는 만류하는 딸을 뒤로한 채 우주선에 탑승하는데...</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"타인의 꿈에 들어가 생각을 훔치는 특수 보안요원 코브. 그를 이용해 라이벌 기업의 정보를 빼내고자 하는 사이토는 코브에게 생각을 훔치는 것이  아닌, 생각을 심는 ‘인셉션’ 작전을 제안한다. 성공 조건으로 국제적인 수배자가 되어있는 코브의 신분을 바꿔주겠다는 거부할 수 없는 제안을 하고, 사랑하는 아이들에게 돌 아가기 위해 그 제안을 받아들인다. 최강의 팀을 구성, 표적인 피셔에게 접근해서 ‘인셉션’ 작전을 실행하지만 예기치 못한 사건들과 마주하게 되는데… 꿈 VS 현실! 시간, 규 칙, 타이밍 모든 것이 완벽해야만 하는, 단 한 번도 성공한 적 없는 ‘인셉션’ 작전이 시작된다!"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fight Club</t>
+  </si>
+  <si>
+    <t>Pulp Fiction</t>
+  </si>
+  <si>
+    <t>The Dark Knight</t>
+  </si>
+  <si>
+    <t>Forrest Gump</t>
+  </si>
+  <si>
+    <t>The Lord of the Rings: The Return of the King</t>
+  </si>
+  <si>
+    <t>The Avengers</t>
+  </si>
+  <si>
+    <t>Avengers: Endgame</t>
+  </si>
+  <si>
+    <t>Whiplash</t>
+  </si>
+  <si>
+    <t>The Shawshank Redemption</t>
+  </si>
+  <si>
+    <t>The Dark Knight Rises</t>
+  </si>
+  <si>
+    <t>Schindler's List</t>
+  </si>
+  <si>
+    <t>The Green Mile</t>
+  </si>
+  <si>
+    <t>"1994-09-10"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"1999-10-15"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"2012-04-25"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"2019-04-24"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"2014-10-10"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"1994-09-23"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"1999-12-10"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"1994-06-23"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"2003-12-17"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>The Matrix</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"2008-07-17"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"1993-12-15"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Star Trek III: The Search for Spock</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Il buono, il brutto, il cattivo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"1966-12-22"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"1999-03-31"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"2012-07-17"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"1984-06-01"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -164,7 +384,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -177,9 +397,6 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -189,17 +406,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -535,39 +749,42 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F419AF50-FB45-4D5E-9164-4A7644DBC1D1}">
-  <dimension ref="B2:G34"/>
+  <dimension ref="B2:H29"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.7265625" customWidth="1"/>
     <col min="3" max="3" width="8.54296875" customWidth="1"/>
-    <col min="4" max="4" width="17.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36.90625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20.1796875" customWidth="1"/>
     <col min="6" max="6" width="18.81640625" customWidth="1"/>
-    <col min="7" max="7" width="35.453125" customWidth="1"/>
+    <col min="7" max="7" width="35.453125" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:8" ht="17.399999999999999" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="5" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="2:7" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="B3" s="5">
+      <c r="H2" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="2:8" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="B3" s="4">
         <v>1</v>
       </c>
       <c r="C3" s="1">
@@ -576,205 +793,329 @@
       <c r="D3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="3">
-        <v>26372</v>
+      <c r="E3" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="F3" s="1">
         <v>8.6999999999999993</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="B4" s="4">
+        <v>2</v>
+      </c>
+      <c r="C4" s="4">
+        <v>27205</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B4" s="5">
-        <v>2</v>
-      </c>
-      <c r="C4">
-        <v>27205</v>
-      </c>
-      <c r="D4" s="8" t="s">
+      <c r="E4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="7">
+        <v>7.5</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="B5" s="4">
+        <v>3</v>
+      </c>
+      <c r="C5" s="4">
+        <v>157336</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>8</v>
-      </c>
-      <c r="E4" s="9">
-        <v>40374</v>
-      </c>
-      <c r="F4" s="10">
-        <v>7.5</v>
-      </c>
-      <c r="G4" s="5"/>
-    </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="5">
-        <v>3</v>
-      </c>
-      <c r="C5">
-        <v>157336</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="3">
-        <v>41948</v>
       </c>
       <c r="F5" s="1">
         <v>8.1999999999999993</v>
       </c>
-      <c r="G5" s="1"/>
-    </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="5">
-        <v>4</v>
-      </c>
-      <c r="C6" s="1"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
+      <c r="G5" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" s="9" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="B6" s="1">
+        <v>5</v>
+      </c>
+      <c r="C6" s="1">
+        <v>550</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F6" s="4">
+        <v>8.4</v>
+      </c>
       <c r="G6" s="1"/>
     </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="5">
-        <v>5</v>
-      </c>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
+    <row r="7" spans="2:8" s="9" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="B7" s="1">
+        <v>6</v>
+      </c>
+      <c r="C7" s="1">
+        <v>680</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F7" s="4">
+        <v>8.5</v>
+      </c>
       <c r="G7" s="1"/>
     </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="5">
-        <v>6</v>
-      </c>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
+    <row r="8" spans="2:8" s="9" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="B8" s="1">
+        <v>8</v>
+      </c>
+      <c r="C8" s="1">
+        <v>155</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F8" s="4">
+        <v>8.5</v>
+      </c>
       <c r="G8" s="1"/>
     </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="5">
+    <row r="9" spans="2:8" s="9" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="B9" s="1">
+        <v>9</v>
+      </c>
+      <c r="C9" s="1">
+        <v>13</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F9" s="4">
+        <v>8.5</v>
+      </c>
+      <c r="G9" s="1"/>
+    </row>
+    <row r="10" spans="2:8" s="9" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="B10" s="1">
+        <v>10</v>
+      </c>
+      <c r="C10" s="1">
+        <v>122</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F10" s="4">
+        <v>8.5</v>
+      </c>
+      <c r="G10" s="1"/>
+    </row>
+    <row r="11" spans="2:8" s="9" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="B11" s="1">
+        <v>11</v>
+      </c>
+      <c r="C11" s="1">
+        <v>157</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F11" s="4">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="G11" s="1"/>
+    </row>
+    <row r="12" spans="2:8" s="9" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="B12" s="1">
+        <v>12</v>
+      </c>
+      <c r="C12" s="1">
+        <v>24428</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F12" s="4">
+        <v>7.7</v>
+      </c>
+      <c r="G12" s="1"/>
+    </row>
+    <row r="13" spans="2:8" s="9" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="B13" s="1">
+        <v>13</v>
+      </c>
+      <c r="C13" s="1">
+        <v>299534</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F13" s="4">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="G13" s="1"/>
+    </row>
+    <row r="14" spans="2:8" s="9" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="B14" s="1">
+        <v>14</v>
+      </c>
+      <c r="C14" s="1">
+        <v>244786</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F14" s="4">
+        <v>8.4</v>
+      </c>
+      <c r="G14" s="1"/>
+    </row>
+    <row r="15" spans="2:8" s="9" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="B15" s="1">
+        <v>15</v>
+      </c>
+      <c r="C15" s="1">
+        <v>278</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F15" s="4">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="G15" s="1"/>
+    </row>
+    <row r="16" spans="2:8" s="9" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="B16" s="1">
+        <v>17</v>
+      </c>
+      <c r="C16" s="1">
+        <v>49026</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F16" s="4">
+        <v>7.7</v>
+      </c>
+      <c r="G16" s="1"/>
+    </row>
+    <row r="17" spans="2:7" s="9" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="B17" s="1">
+        <v>18</v>
+      </c>
+      <c r="C17" s="1">
+        <v>424</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F17" s="4">
+        <v>8.6</v>
+      </c>
+      <c r="G17" s="1"/>
+    </row>
+    <row r="18" spans="2:7" s="9" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="B18" s="1">
+        <v>19</v>
+      </c>
+      <c r="C18" s="1">
+        <v>603</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F18" s="4">
         <v>7</v>
       </c>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-    </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="5">
-        <v>8</v>
-      </c>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-    </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B11" s="5">
-        <v>9</v>
-      </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-    </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="5">
-        <v>10</v>
-      </c>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-    </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="5">
-        <v>11</v>
-      </c>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-    </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="5">
-        <v>12</v>
-      </c>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-    </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="5">
-        <v>13</v>
-      </c>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-    </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="5">
-        <v>14</v>
-      </c>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="5">
-        <v>15</v>
-      </c>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-    </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B18" s="5">
-        <v>16</v>
-      </c>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
       <c r="G18" s="1"/>
     </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="5">
-        <v>17</v>
-      </c>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
+    <row r="19" spans="2:7" s="9" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="B19" s="1">
+        <v>21</v>
+      </c>
+      <c r="C19" s="1">
+        <v>429</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F19" s="4">
+        <v>8.5</v>
+      </c>
       <c r="G19" s="1"/>
     </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B20" s="5">
-        <v>18</v>
-      </c>
-      <c r="C20" s="4"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
+    <row r="20" spans="2:7" s="9" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="B20" s="1">
+        <v>22</v>
+      </c>
+      <c r="C20" s="1">
+        <v>497</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F20" s="4">
+        <v>8.5</v>
+      </c>
       <c r="G20" s="1"/>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B21" s="5">
-        <v>19</v>
+      <c r="B21" s="4">
+        <v>24</v>
       </c>
       <c r="C21" s="4"/>
       <c r="D21" s="1"/>
@@ -783,8 +1124,8 @@
       <c r="G21" s="1"/>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B22" s="5">
-        <v>20</v>
+      <c r="B22" s="4">
+        <v>25</v>
       </c>
       <c r="C22" s="4"/>
       <c r="D22" s="1"/>
@@ -793,8 +1134,8 @@
       <c r="G22" s="1"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B23" s="5">
-        <v>21</v>
+      <c r="B23" s="4">
+        <v>26</v>
       </c>
       <c r="C23" s="4"/>
       <c r="D23" s="1"/>
@@ -803,8 +1144,8 @@
       <c r="G23" s="1"/>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B24" s="5">
-        <v>22</v>
+      <c r="B24" s="4">
+        <v>27</v>
       </c>
       <c r="C24" s="4"/>
       <c r="D24" s="1"/>
@@ -813,8 +1154,8 @@
       <c r="G24" s="1"/>
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B25" s="5">
-        <v>23</v>
+      <c r="B25" s="4">
+        <v>28</v>
       </c>
       <c r="C25" s="4"/>
       <c r="D25" s="1"/>
@@ -823,94 +1164,44 @@
       <c r="G25" s="1"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B26" s="5">
-        <v>24</v>
-      </c>
-      <c r="C26" s="5"/>
+      <c r="B26" s="4">
+        <v>29</v>
+      </c>
+      <c r="C26" s="4"/>
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B27" s="5">
-        <v>25</v>
-      </c>
-      <c r="C27" s="5"/>
+      <c r="B27" s="4">
+        <v>30</v>
+      </c>
+      <c r="C27" s="4"/>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B28" s="5">
-        <v>26</v>
-      </c>
-      <c r="C28" s="5"/>
+      <c r="B28" s="4">
+        <v>31</v>
+      </c>
+      <c r="C28" s="4"/>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B29" s="5">
-        <v>27</v>
-      </c>
-      <c r="C29" s="5"/>
+      <c r="B29" s="4">
+        <v>32</v>
+      </c>
+      <c r="C29" s="4"/>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
-      <c r="G29" s="1"/>
-    </row>
-    <row r="30" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B30" s="5">
-        <v>28</v>
-      </c>
-      <c r="C30" s="5"/>
-      <c r="D30" s="1"/>
-      <c r="E30" s="1"/>
-      <c r="F30" s="1"/>
-      <c r="G30" s="1"/>
-    </row>
-    <row r="31" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B31" s="5">
-        <v>29</v>
-      </c>
-      <c r="C31" s="5"/>
-      <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
-      <c r="F31" s="1"/>
-      <c r="G31" s="1"/>
-    </row>
-    <row r="32" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B32" s="5">
-        <v>30</v>
-      </c>
-      <c r="C32" s="5"/>
-      <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
-      <c r="F32" s="1"/>
-      <c r="G32" s="1"/>
-    </row>
-    <row r="33" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B33" s="5">
-        <v>31</v>
-      </c>
-      <c r="C33" s="5"/>
-      <c r="D33" s="1"/>
-      <c r="E33" s="1"/>
-      <c r="F33" s="1"/>
-      <c r="G33" s="1"/>
-    </row>
-    <row r="34" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B34" s="5">
-        <v>32</v>
-      </c>
-      <c r="C34" s="5"/>
-      <c r="D34" s="1"/>
-      <c r="E34" s="1"/>
-      <c r="F34" s="1"/>
-      <c r="G34" s="5"/>
+      <c r="G29" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
